--- a/docs/bp/Modelo-Economico-Piumhi.xlsx
+++ b/docs/bp/Modelo-Economico-Piumhi.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Premissas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fluxo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Capital" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fluxo" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,9 +130,12 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -927,351 +931,396 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Pro-labore do operador</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>um negocio que so fecha com o dono de graca nao fechou</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>TOTAL FIXO</t>
         </is>
       </c>
-      <c r="B46" s="15">
-        <f>SUM(B36:B45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="B47" s="15">
+        <f>SUM(B36:B46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>CAPEX DE IMPLANTACAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Cambio de planejamento (R$/USD)</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Focus fim-2026: 5,20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Maquina JM-70 posta em Piumhi (USD 23.000)</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>121900</v>
+          <t>Cambio de planejamento (R$/USD)</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Focus fim-2026: 5,20</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Interface Modbus/API + kit de pecas 2 anos (USD 2.000)</t>
+          <t>Maquina JM-70 posta em Piumhi (USD 23.000)</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>10600</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Obra civil: portico, baia coberta, piso, patio 300 m2</t>
+          <t>Interface Modbus/API + kit de pecas 2 anos (USD 2.000)</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>92000</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Caixa separadora agua/oleo + hidraulica + reservatorio</t>
+          <t>Obra civil: portico, baia coberta, piso, patio 300 m2</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>26000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Entrada de energia, quadro, cabeamento, projeto e ART</t>
+          <t>Caixa separadora agua/oleo + hidraulica + reservatorio</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>24000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Laudo NR-12 com ART</t>
+          <t>Entrada de energia, quadro, cabeamento, projeto e ART</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>6000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Totem de pagamento PIX/cartao + camera + CFTV + rede</t>
+          <t>Laudo NR-12 com ART</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>26000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>1 box de alta pressao + 2 aspiradores</t>
+          <t>Totem de pagamento PIX/cartao + camera + CFTV + rede</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>18000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Fachada, comunicacao visual, iluminacao</t>
+          <t>1 box de alta pressao + 2 aspiradores</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>19000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Software da unidade, integracao e implantacao</t>
+          <t>Fachada, comunicacao visual, iluminacao</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>12000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
+          <t>Software da unidade, integracao e implantacao</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>Projeto, licencas, alvaras, bombeiros, taxas</t>
         </is>
       </c>
-      <c r="B60" s="8" t="n">
+      <c r="B61" s="8" t="n">
         <v>14000</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B61" s="16">
-        <f>SUM(B50:B60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="B62" s="16">
+        <f>SUM(B51:B61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Contingencia (%)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n">
+      <c r="B63" s="12" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Cortes da versao enxuta</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>71060</v>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>boxes e aspiradores no mes 6, patio de 150 m2, fachada simples; zere para o capex cheio</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>CAPEX TOTAL</t>
         </is>
       </c>
-      <c r="B63" s="15">
-        <f>B61*(1+B62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B65" s="15">
+        <f>B62*(1+B63)-B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>do qual benfeitoria em imovel de terceiro</t>
         </is>
       </c>
-      <c r="B64" s="17">
-        <f>B52+B53+B54</f>
-        <v/>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="B66" s="17">
+        <f>B53+B54+B55</f>
+        <v/>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>obra civil + separadora + entrada de energia</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>CAPITAL DE GIRO</t>
         </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Caucao de 3 alugueis</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Campanha de pre-venda e inauguracao</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>22000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Estoque inicial de quimicos</t>
+          <t>Caucao de 3 alugueis</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>Campanha de pre-venda e inauguracao</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Estoque inicial de quimicos</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t>Colchao de 3 meses de custo fixo</t>
         </is>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B72" s="8" t="n">
         <v>18000</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL GIRO</t>
-        </is>
-      </c>
-      <c r="B71" s="15">
-        <f>SUM(B67:B70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t>INVESTIMENTO TOTAL</t>
-        </is>
-      </c>
-      <c r="B72" s="19">
-        <f>B63+B71</f>
-        <v/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Cortes no giro (versao enxuta)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>zere junto com os cortes do capex</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>TOTAL GIRO</t>
+        </is>
+      </c>
+      <c r="B74" s="15">
+        <f>SUM(B69:B72)-B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>INVESTIMENTO TOTAL</t>
+        </is>
+      </c>
+      <c r="B75" s="19">
+        <f>B65+B74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>FINANCEIRO</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>TMA (a.a.)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B78" s="12" t="n">
         <v>0.18</v>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Selic em ago/2026: 14% a.a.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Capex de manutencao (% da receita)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B79" s="12" t="n">
         <v>0.015</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Valor residual do capex no mes 60</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>CAPACIDADE</t>
-        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ciclo + manobra (min)</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Disponibilidade da maquina</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="n">
-        <v>0.9</v>
+          <t>Valor residual do capex no mes 60</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Janela diaria de pico (horas)</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="n">
-        <v>13</v>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>CAPACIDADE</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
+          <t>Ciclo + manobra (min)</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Disponibilidade da maquina</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Janela diaria de pico (horas)</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>Lavagens na janela de pico</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n">
+      <c r="B86" s="12" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1311,7 +1360,7 @@
         </is>
       </c>
       <c r="B3" s="19">
-        <f>Premissas!$B$72</f>
+        <f>Premissas!$B$75</f>
         <v/>
       </c>
     </row>
@@ -1322,7 +1371,7 @@
         </is>
       </c>
       <c r="B4" s="17">
-        <f>Premissas!$B$63</f>
+        <f>Premissas!$B$65</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1382,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Premissas!$B$71</f>
+        <f>Premissas!$B$74</f>
         <v/>
       </c>
     </row>
@@ -1344,7 +1393,7 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>Premissas!$B$64</f>
+        <f>Premissas!$B$66</f>
         <v/>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1420,7 +1469,7 @@
         </is>
       </c>
       <c r="B14" s="19">
-        <f>NPV((1+Premissas!$B$75)^(1/12)-1,Fluxo!$R$5:$R$64)+Fluxo!$R$4</f>
+        <f>NPV((1+Premissas!$B$78)^(1/12)-1,Fluxo!$R$5:$R$64)+Fluxo!$R$4</f>
         <v/>
       </c>
     </row>
@@ -1442,7 +1491,7 @@
         </is>
       </c>
       <c r="B16" s="21">
-        <f>SUM(Fluxo!$R$5:$R$64)/Premissas!$B$72</f>
+        <f>SUM(Fluxo!$R$5:$R$64)/Premissas!$B$75</f>
         <v/>
       </c>
     </row>
@@ -1471,7 +1520,7 @@
         </is>
       </c>
       <c r="B20" s="17">
-        <f>Premissas!$B$46/(1-Fluxo!K64-Fluxo!M64/Fluxo!G64)</f>
+        <f>Premissas!$B$47/(1-Fluxo!K64-Fluxo!M64/Fluxo!G64)</f>
         <v/>
       </c>
     </row>
@@ -1511,7 +1560,7 @@
         </is>
       </c>
       <c r="B25" s="20">
-        <f>60/Premissas!$B$80*Premissas!$B$81*Premissas!$B$82/Premissas!$B$83</f>
+        <f>60/Premissas!$B$83*Premissas!$B$84*Premissas!$B$85/Premissas!$B$86</f>
         <v/>
       </c>
     </row>
@@ -1544,6 +1593,2726 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ESTRUTURA DE CAPITAL  |  divida, pre-venda e divisao entre socios</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Celulas em bege sao de entrada. O resto e formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>DIVIDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Valor da divida</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>cooperativa de credito local e a fonte mais provavel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Juros (a.a.)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Prazo (meses)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Carencia (meses, so juros)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>exija 6 no minimo: os meses 1 a 4 tem EBITDA negativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juros mensais</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>(1+B7)^(1/12)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Parcela apos a carencia</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>B6*B10/(1-(1+B10)^-B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Juros durante a carencia</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>B6*B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PRE-VENDA ANUAL DOS FUNDADORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Numero de fundadores</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Mensalidade do fundador</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Meses pagos a vista</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>12 meses pelo preco de 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Caixa no mes 0</t>
+        </is>
+      </c>
+      <c r="B18" s="15">
+        <f>B15*B16*B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DIVISAO DO EQUITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Aporte do investidor A</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Fatia do investidor A</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Aporte do investidor B</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Fatia do investidor B</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>FCL do projeto</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Servico da divida</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>Ajuste da pre-venda</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>FCL do equity</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Caixa acumulado</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>Investidor A</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>Investidor B</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="17">
+        <f>Fluxo!$R$4</f>
+        <v/>
+      </c>
+      <c r="C27" s="17">
+        <f>-Capital!$B$6</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>-Capital!$B$18</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>B27-C27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>-Capital!$B$21</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>-Capital!$B$23</f>
+        <v/>
+      </c>
+      <c r="I27" s="17">
+        <f>-(MIN(F27:F87)*-1-Capital!$B$21-Capital!$B$23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="17">
+        <f>Fluxo!$R$5</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>IF(A28&lt;=Capital!$B$9,Capital!$B$12,IF(A28&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>IF(A28&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$5),0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>B28-C28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>F27+E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f>E28*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>E28*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>E28*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="17">
+        <f>Fluxo!$R$6</f>
+        <v/>
+      </c>
+      <c r="C29" s="17">
+        <f>IF(A29&lt;=Capital!$B$9,Capital!$B$12,IF(A29&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>IF(A29&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$6),0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>B29-C29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>F28+E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>E29*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>E29*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>E29*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="17">
+        <f>Fluxo!$R$7</f>
+        <v/>
+      </c>
+      <c r="C30" s="17">
+        <f>IF(A30&lt;=Capital!$B$9,Capital!$B$12,IF(A30&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D30" s="17">
+        <f>IF(A30&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$7),0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="17">
+        <f>B30-C30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="17">
+        <f>F29+E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f>E30*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>E30*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I30" s="17">
+        <f>E30*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="17">
+        <f>Fluxo!$R$8</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>IF(A31&lt;=Capital!$B$9,Capital!$B$12,IF(A31&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>IF(A31&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$8),0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>B31-C31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>F30+E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>E31*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>E31*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>E31*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="17">
+        <f>Fluxo!$R$9</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>IF(A32&lt;=Capital!$B$9,Capital!$B$12,IF(A32&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>IF(A32&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$9),0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>B32-C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>F31+E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>E32*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>E32*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>E32*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="17">
+        <f>Fluxo!$R$10</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>IF(A33&lt;=Capital!$B$9,Capital!$B$12,IF(A33&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>IF(A33&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$10),0)</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>B33-C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>F32+E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>E33*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>E33*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>E33*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="17">
+        <f>Fluxo!$R$11</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>IF(A34&lt;=Capital!$B$9,Capital!$B$12,IF(A34&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>IF(A34&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$11),0)</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>B34-C34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>F33+E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>E34*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>E34*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>E34*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="17">
+        <f>Fluxo!$R$12</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>IF(A35&lt;=Capital!$B$9,Capital!$B$12,IF(A35&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>IF(A35&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$12),0)</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>B35-C35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>F34+E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>E35*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>E35*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>E35*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="17">
+        <f>Fluxo!$R$13</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>IF(A36&lt;=Capital!$B$9,Capital!$B$12,IF(A36&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>IF(A36&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$13),0)</f>
+        <v/>
+      </c>
+      <c r="E36" s="17">
+        <f>B36-C36-D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>F35+E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>E36*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>E36*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>E36*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="17">
+        <f>Fluxo!$R$14</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>IF(A37&lt;=Capital!$B$9,Capital!$B$12,IF(A37&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>IF(A37&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$14),0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>B37-C37-D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>F36+E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>E37*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>E37*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>E37*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="17">
+        <f>Fluxo!$R$15</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>IF(A38&lt;=Capital!$B$9,Capital!$B$12,IF(A38&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>IF(A38&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$15),0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>B38-C38-D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>F37+E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>E38*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>E38*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I38" s="17">
+        <f>E38*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="17">
+        <f>Fluxo!$R$16</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>IF(A39&lt;=Capital!$B$9,Capital!$B$12,IF(A39&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>IF(A39&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$16),0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>B39-C39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>F38+E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>E39*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>E39*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>E39*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="17">
+        <f>Fluxo!$R$17</f>
+        <v/>
+      </c>
+      <c r="C40" s="17">
+        <f>IF(A40&lt;=Capital!$B$9,Capital!$B$12,IF(A40&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>IF(A40&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$17),0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>B40-C40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>F39+E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="17">
+        <f>E40*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>E40*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I40" s="17">
+        <f>E40*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" s="17">
+        <f>Fluxo!$R$18</f>
+        <v/>
+      </c>
+      <c r="C41" s="17">
+        <f>IF(A41&lt;=Capital!$B$9,Capital!$B$12,IF(A41&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>IF(A41&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$18),0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>B41-C41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>F40+E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>E41*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>E41*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>E41*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="17">
+        <f>Fluxo!$R$19</f>
+        <v/>
+      </c>
+      <c r="C42" s="17">
+        <f>IF(A42&lt;=Capital!$B$9,Capital!$B$12,IF(A42&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>IF(A42&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$19),0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f>B42-C42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="17">
+        <f>F41+E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="17">
+        <f>E42*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>E42*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I42" s="17">
+        <f>E42*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" s="17">
+        <f>Fluxo!$R$20</f>
+        <v/>
+      </c>
+      <c r="C43" s="17">
+        <f>IF(A43&lt;=Capital!$B$9,Capital!$B$12,IF(A43&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>IF(A43&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$20),0)</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>B43-C43-D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>F42+E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>E43*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>E43*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I43" s="17">
+        <f>E43*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" s="17">
+        <f>Fluxo!$R$21</f>
+        <v/>
+      </c>
+      <c r="C44" s="17">
+        <f>IF(A44&lt;=Capital!$B$9,Capital!$B$12,IF(A44&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>IF(A44&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$21),0)</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>B44-C44-D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>F43+E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>E44*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>E44*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I44" s="17">
+        <f>E44*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="17">
+        <f>Fluxo!$R$22</f>
+        <v/>
+      </c>
+      <c r="C45" s="17">
+        <f>IF(A45&lt;=Capital!$B$9,Capital!$B$12,IF(A45&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>IF(A45&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$22),0)</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>B45-C45-D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>F44+E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>E45*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>E45*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I45" s="17">
+        <f>E45*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="17">
+        <f>Fluxo!$R$23</f>
+        <v/>
+      </c>
+      <c r="C46" s="17">
+        <f>IF(A46&lt;=Capital!$B$9,Capital!$B$12,IF(A46&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>IF(A46&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$23),0)</f>
+        <v/>
+      </c>
+      <c r="E46" s="17">
+        <f>B46-C46-D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>F45+E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>E46*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>E46*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I46" s="17">
+        <f>E46*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>20</v>
+      </c>
+      <c r="B47" s="17">
+        <f>Fluxo!$R$24</f>
+        <v/>
+      </c>
+      <c r="C47" s="17">
+        <f>IF(A47&lt;=Capital!$B$9,Capital!$B$12,IF(A47&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>IF(A47&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$24),0)</f>
+        <v/>
+      </c>
+      <c r="E47" s="17">
+        <f>B47-C47-D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>F46+E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>E47*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>E47*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I47" s="17">
+        <f>E47*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>21</v>
+      </c>
+      <c r="B48" s="17">
+        <f>Fluxo!$R$25</f>
+        <v/>
+      </c>
+      <c r="C48" s="17">
+        <f>IF(A48&lt;=Capital!$B$9,Capital!$B$12,IF(A48&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D48" s="17">
+        <f>IF(A48&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$25),0)</f>
+        <v/>
+      </c>
+      <c r="E48" s="17">
+        <f>B48-C48-D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>F47+E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>E48*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>E48*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I48" s="17">
+        <f>E48*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>22</v>
+      </c>
+      <c r="B49" s="17">
+        <f>Fluxo!$R$26</f>
+        <v/>
+      </c>
+      <c r="C49" s="17">
+        <f>IF(A49&lt;=Capital!$B$9,Capital!$B$12,IF(A49&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>IF(A49&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$26),0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="17">
+        <f>B49-C49-D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>F48+E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>E49*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>E49*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I49" s="17">
+        <f>E49*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>23</v>
+      </c>
+      <c r="B50" s="17">
+        <f>Fluxo!$R$27</f>
+        <v/>
+      </c>
+      <c r="C50" s="17">
+        <f>IF(A50&lt;=Capital!$B$9,Capital!$B$12,IF(A50&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D50" s="17">
+        <f>IF(A50&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$27),0)</f>
+        <v/>
+      </c>
+      <c r="E50" s="17">
+        <f>B50-C50-D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="17">
+        <f>F49+E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="17">
+        <f>E50*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H50" s="17">
+        <f>E50*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I50" s="17">
+        <f>E50*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>24</v>
+      </c>
+      <c r="B51" s="17">
+        <f>Fluxo!$R$28</f>
+        <v/>
+      </c>
+      <c r="C51" s="17">
+        <f>IF(A51&lt;=Capital!$B$9,Capital!$B$12,IF(A51&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D51" s="17">
+        <f>IF(A51&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$28),0)</f>
+        <v/>
+      </c>
+      <c r="E51" s="17">
+        <f>B51-C51-D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="17">
+        <f>F50+E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>E51*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H51" s="17">
+        <f>E51*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I51" s="17">
+        <f>E51*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>25</v>
+      </c>
+      <c r="B52" s="17">
+        <f>Fluxo!$R$29</f>
+        <v/>
+      </c>
+      <c r="C52" s="17">
+        <f>IF(A52&lt;=Capital!$B$9,Capital!$B$12,IF(A52&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D52" s="17">
+        <f>IF(A52&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$29),0)</f>
+        <v/>
+      </c>
+      <c r="E52" s="17">
+        <f>B52-C52-D52</f>
+        <v/>
+      </c>
+      <c r="F52" s="17">
+        <f>F51+E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="17">
+        <f>E52*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H52" s="17">
+        <f>E52*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I52" s="17">
+        <f>E52*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>26</v>
+      </c>
+      <c r="B53" s="17">
+        <f>Fluxo!$R$30</f>
+        <v/>
+      </c>
+      <c r="C53" s="17">
+        <f>IF(A53&lt;=Capital!$B$9,Capital!$B$12,IF(A53&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D53" s="17">
+        <f>IF(A53&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$30),0)</f>
+        <v/>
+      </c>
+      <c r="E53" s="17">
+        <f>B53-C53-D53</f>
+        <v/>
+      </c>
+      <c r="F53" s="17">
+        <f>F52+E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="17">
+        <f>E53*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H53" s="17">
+        <f>E53*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I53" s="17">
+        <f>E53*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>27</v>
+      </c>
+      <c r="B54" s="17">
+        <f>Fluxo!$R$31</f>
+        <v/>
+      </c>
+      <c r="C54" s="17">
+        <f>IF(A54&lt;=Capital!$B$9,Capital!$B$12,IF(A54&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D54" s="17">
+        <f>IF(A54&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$31),0)</f>
+        <v/>
+      </c>
+      <c r="E54" s="17">
+        <f>B54-C54-D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="17">
+        <f>F53+E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="17">
+        <f>E54*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H54" s="17">
+        <f>E54*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I54" s="17">
+        <f>E54*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>28</v>
+      </c>
+      <c r="B55" s="17">
+        <f>Fluxo!$R$32</f>
+        <v/>
+      </c>
+      <c r="C55" s="17">
+        <f>IF(A55&lt;=Capital!$B$9,Capital!$B$12,IF(A55&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D55" s="17">
+        <f>IF(A55&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$32),0)</f>
+        <v/>
+      </c>
+      <c r="E55" s="17">
+        <f>B55-C55-D55</f>
+        <v/>
+      </c>
+      <c r="F55" s="17">
+        <f>F54+E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="17">
+        <f>E55*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H55" s="17">
+        <f>E55*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I55" s="17">
+        <f>E55*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>29</v>
+      </c>
+      <c r="B56" s="17">
+        <f>Fluxo!$R$33</f>
+        <v/>
+      </c>
+      <c r="C56" s="17">
+        <f>IF(A56&lt;=Capital!$B$9,Capital!$B$12,IF(A56&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D56" s="17">
+        <f>IF(A56&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$33),0)</f>
+        <v/>
+      </c>
+      <c r="E56" s="17">
+        <f>B56-C56-D56</f>
+        <v/>
+      </c>
+      <c r="F56" s="17">
+        <f>F55+E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="17">
+        <f>E56*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H56" s="17">
+        <f>E56*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I56" s="17">
+        <f>E56*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>30</v>
+      </c>
+      <c r="B57" s="17">
+        <f>Fluxo!$R$34</f>
+        <v/>
+      </c>
+      <c r="C57" s="17">
+        <f>IF(A57&lt;=Capital!$B$9,Capital!$B$12,IF(A57&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D57" s="17">
+        <f>IF(A57&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$34),0)</f>
+        <v/>
+      </c>
+      <c r="E57" s="17">
+        <f>B57-C57-D57</f>
+        <v/>
+      </c>
+      <c r="F57" s="17">
+        <f>F56+E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="17">
+        <f>E57*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H57" s="17">
+        <f>E57*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I57" s="17">
+        <f>E57*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>31</v>
+      </c>
+      <c r="B58" s="17">
+        <f>Fluxo!$R$35</f>
+        <v/>
+      </c>
+      <c r="C58" s="17">
+        <f>IF(A58&lt;=Capital!$B$9,Capital!$B$12,IF(A58&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D58" s="17">
+        <f>IF(A58&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$35),0)</f>
+        <v/>
+      </c>
+      <c r="E58" s="17">
+        <f>B58-C58-D58</f>
+        <v/>
+      </c>
+      <c r="F58" s="17">
+        <f>F57+E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="17">
+        <f>E58*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H58" s="17">
+        <f>E58*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I58" s="17">
+        <f>E58*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>32</v>
+      </c>
+      <c r="B59" s="17">
+        <f>Fluxo!$R$36</f>
+        <v/>
+      </c>
+      <c r="C59" s="17">
+        <f>IF(A59&lt;=Capital!$B$9,Capital!$B$12,IF(A59&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D59" s="17">
+        <f>IF(A59&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$36),0)</f>
+        <v/>
+      </c>
+      <c r="E59" s="17">
+        <f>B59-C59-D59</f>
+        <v/>
+      </c>
+      <c r="F59" s="17">
+        <f>F58+E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="17">
+        <f>E59*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H59" s="17">
+        <f>E59*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I59" s="17">
+        <f>E59*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>33</v>
+      </c>
+      <c r="B60" s="17">
+        <f>Fluxo!$R$37</f>
+        <v/>
+      </c>
+      <c r="C60" s="17">
+        <f>IF(A60&lt;=Capital!$B$9,Capital!$B$12,IF(A60&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D60" s="17">
+        <f>IF(A60&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$37),0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="17">
+        <f>B60-C60-D60</f>
+        <v/>
+      </c>
+      <c r="F60" s="17">
+        <f>F59+E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="17">
+        <f>E60*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H60" s="17">
+        <f>E60*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I60" s="17">
+        <f>E60*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>34</v>
+      </c>
+      <c r="B61" s="17">
+        <f>Fluxo!$R$38</f>
+        <v/>
+      </c>
+      <c r="C61" s="17">
+        <f>IF(A61&lt;=Capital!$B$9,Capital!$B$12,IF(A61&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D61" s="17">
+        <f>IF(A61&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$38),0)</f>
+        <v/>
+      </c>
+      <c r="E61" s="17">
+        <f>B61-C61-D61</f>
+        <v/>
+      </c>
+      <c r="F61" s="17">
+        <f>F60+E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="17">
+        <f>E61*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H61" s="17">
+        <f>E61*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I61" s="17">
+        <f>E61*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>35</v>
+      </c>
+      <c r="B62" s="17">
+        <f>Fluxo!$R$39</f>
+        <v/>
+      </c>
+      <c r="C62" s="17">
+        <f>IF(A62&lt;=Capital!$B$9,Capital!$B$12,IF(A62&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D62" s="17">
+        <f>IF(A62&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$39),0)</f>
+        <v/>
+      </c>
+      <c r="E62" s="17">
+        <f>B62-C62-D62</f>
+        <v/>
+      </c>
+      <c r="F62" s="17">
+        <f>F61+E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="17">
+        <f>E62*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H62" s="17">
+        <f>E62*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I62" s="17">
+        <f>E62*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>36</v>
+      </c>
+      <c r="B63" s="17">
+        <f>Fluxo!$R$40</f>
+        <v/>
+      </c>
+      <c r="C63" s="17">
+        <f>IF(A63&lt;=Capital!$B$9,Capital!$B$12,IF(A63&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D63" s="17">
+        <f>IF(A63&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$40),0)</f>
+        <v/>
+      </c>
+      <c r="E63" s="17">
+        <f>B63-C63-D63</f>
+        <v/>
+      </c>
+      <c r="F63" s="17">
+        <f>F62+E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="17">
+        <f>E63*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H63" s="17">
+        <f>E63*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I63" s="17">
+        <f>E63*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>37</v>
+      </c>
+      <c r="B64" s="17">
+        <f>Fluxo!$R$41</f>
+        <v/>
+      </c>
+      <c r="C64" s="17">
+        <f>IF(A64&lt;=Capital!$B$9,Capital!$B$12,IF(A64&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D64" s="17">
+        <f>IF(A64&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$41),0)</f>
+        <v/>
+      </c>
+      <c r="E64" s="17">
+        <f>B64-C64-D64</f>
+        <v/>
+      </c>
+      <c r="F64" s="17">
+        <f>F63+E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="17">
+        <f>E64*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H64" s="17">
+        <f>E64*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I64" s="17">
+        <f>E64*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>38</v>
+      </c>
+      <c r="B65" s="17">
+        <f>Fluxo!$R$42</f>
+        <v/>
+      </c>
+      <c r="C65" s="17">
+        <f>IF(A65&lt;=Capital!$B$9,Capital!$B$12,IF(A65&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(A65&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$42),0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="17">
+        <f>B65-C65-D65</f>
+        <v/>
+      </c>
+      <c r="F65" s="17">
+        <f>F64+E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="17">
+        <f>E65*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>E65*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>E65*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>39</v>
+      </c>
+      <c r="B66" s="17">
+        <f>Fluxo!$R$43</f>
+        <v/>
+      </c>
+      <c r="C66" s="17">
+        <f>IF(A66&lt;=Capital!$B$9,Capital!$B$12,IF(A66&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(A66&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$43),0)</f>
+        <v/>
+      </c>
+      <c r="E66" s="17">
+        <f>B66-C66-D66</f>
+        <v/>
+      </c>
+      <c r="F66" s="17">
+        <f>F65+E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="17">
+        <f>E66*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>E66*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>E66*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>40</v>
+      </c>
+      <c r="B67" s="17">
+        <f>Fluxo!$R$44</f>
+        <v/>
+      </c>
+      <c r="C67" s="17">
+        <f>IF(A67&lt;=Capital!$B$9,Capital!$B$12,IF(A67&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D67" s="17">
+        <f>IF(A67&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$44),0)</f>
+        <v/>
+      </c>
+      <c r="E67" s="17">
+        <f>B67-C67-D67</f>
+        <v/>
+      </c>
+      <c r="F67" s="17">
+        <f>F66+E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="17">
+        <f>E67*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H67" s="17">
+        <f>E67*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I67" s="17">
+        <f>E67*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>41</v>
+      </c>
+      <c r="B68" s="17">
+        <f>Fluxo!$R$45</f>
+        <v/>
+      </c>
+      <c r="C68" s="17">
+        <f>IF(A68&lt;=Capital!$B$9,Capital!$B$12,IF(A68&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D68" s="17">
+        <f>IF(A68&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$45),0)</f>
+        <v/>
+      </c>
+      <c r="E68" s="17">
+        <f>B68-C68-D68</f>
+        <v/>
+      </c>
+      <c r="F68" s="17">
+        <f>F67+E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="17">
+        <f>E68*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H68" s="17">
+        <f>E68*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I68" s="17">
+        <f>E68*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>42</v>
+      </c>
+      <c r="B69" s="17">
+        <f>Fluxo!$R$46</f>
+        <v/>
+      </c>
+      <c r="C69" s="17">
+        <f>IF(A69&lt;=Capital!$B$9,Capital!$B$12,IF(A69&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D69" s="17">
+        <f>IF(A69&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$46),0)</f>
+        <v/>
+      </c>
+      <c r="E69" s="17">
+        <f>B69-C69-D69</f>
+        <v/>
+      </c>
+      <c r="F69" s="17">
+        <f>F68+E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="17">
+        <f>E69*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H69" s="17">
+        <f>E69*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I69" s="17">
+        <f>E69*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>43</v>
+      </c>
+      <c r="B70" s="17">
+        <f>Fluxo!$R$47</f>
+        <v/>
+      </c>
+      <c r="C70" s="17">
+        <f>IF(A70&lt;=Capital!$B$9,Capital!$B$12,IF(A70&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D70" s="17">
+        <f>IF(A70&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$47),0)</f>
+        <v/>
+      </c>
+      <c r="E70" s="17">
+        <f>B70-C70-D70</f>
+        <v/>
+      </c>
+      <c r="F70" s="17">
+        <f>F69+E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="17">
+        <f>E70*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H70" s="17">
+        <f>E70*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I70" s="17">
+        <f>E70*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>44</v>
+      </c>
+      <c r="B71" s="17">
+        <f>Fluxo!$R$48</f>
+        <v/>
+      </c>
+      <c r="C71" s="17">
+        <f>IF(A71&lt;=Capital!$B$9,Capital!$B$12,IF(A71&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>IF(A71&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$48),0)</f>
+        <v/>
+      </c>
+      <c r="E71" s="17">
+        <f>B71-C71-D71</f>
+        <v/>
+      </c>
+      <c r="F71" s="17">
+        <f>F70+E71</f>
+        <v/>
+      </c>
+      <c r="G71" s="17">
+        <f>E71*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H71" s="17">
+        <f>E71*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I71" s="17">
+        <f>E71*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>45</v>
+      </c>
+      <c r="B72" s="17">
+        <f>Fluxo!$R$49</f>
+        <v/>
+      </c>
+      <c r="C72" s="17">
+        <f>IF(A72&lt;=Capital!$B$9,Capital!$B$12,IF(A72&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D72" s="17">
+        <f>IF(A72&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$49),0)</f>
+        <v/>
+      </c>
+      <c r="E72" s="17">
+        <f>B72-C72-D72</f>
+        <v/>
+      </c>
+      <c r="F72" s="17">
+        <f>F71+E72</f>
+        <v/>
+      </c>
+      <c r="G72" s="17">
+        <f>E72*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H72" s="17">
+        <f>E72*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I72" s="17">
+        <f>E72*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>46</v>
+      </c>
+      <c r="B73" s="17">
+        <f>Fluxo!$R$50</f>
+        <v/>
+      </c>
+      <c r="C73" s="17">
+        <f>IF(A73&lt;=Capital!$B$9,Capital!$B$12,IF(A73&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D73" s="17">
+        <f>IF(A73&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$50),0)</f>
+        <v/>
+      </c>
+      <c r="E73" s="17">
+        <f>B73-C73-D73</f>
+        <v/>
+      </c>
+      <c r="F73" s="17">
+        <f>F72+E73</f>
+        <v/>
+      </c>
+      <c r="G73" s="17">
+        <f>E73*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H73" s="17">
+        <f>E73*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I73" s="17">
+        <f>E73*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>47</v>
+      </c>
+      <c r="B74" s="17">
+        <f>Fluxo!$R$51</f>
+        <v/>
+      </c>
+      <c r="C74" s="17">
+        <f>IF(A74&lt;=Capital!$B$9,Capital!$B$12,IF(A74&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D74" s="17">
+        <f>IF(A74&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$51),0)</f>
+        <v/>
+      </c>
+      <c r="E74" s="17">
+        <f>B74-C74-D74</f>
+        <v/>
+      </c>
+      <c r="F74" s="17">
+        <f>F73+E74</f>
+        <v/>
+      </c>
+      <c r="G74" s="17">
+        <f>E74*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H74" s="17">
+        <f>E74*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I74" s="17">
+        <f>E74*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>48</v>
+      </c>
+      <c r="B75" s="17">
+        <f>Fluxo!$R$52</f>
+        <v/>
+      </c>
+      <c r="C75" s="17">
+        <f>IF(A75&lt;=Capital!$B$9,Capital!$B$12,IF(A75&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D75" s="17">
+        <f>IF(A75&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$52),0)</f>
+        <v/>
+      </c>
+      <c r="E75" s="17">
+        <f>B75-C75-D75</f>
+        <v/>
+      </c>
+      <c r="F75" s="17">
+        <f>F74+E75</f>
+        <v/>
+      </c>
+      <c r="G75" s="17">
+        <f>E75*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H75" s="17">
+        <f>E75*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I75" s="17">
+        <f>E75*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>49</v>
+      </c>
+      <c r="B76" s="17">
+        <f>Fluxo!$R$53</f>
+        <v/>
+      </c>
+      <c r="C76" s="17">
+        <f>IF(A76&lt;=Capital!$B$9,Capital!$B$12,IF(A76&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D76" s="17">
+        <f>IF(A76&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$53),0)</f>
+        <v/>
+      </c>
+      <c r="E76" s="17">
+        <f>B76-C76-D76</f>
+        <v/>
+      </c>
+      <c r="F76" s="17">
+        <f>F75+E76</f>
+        <v/>
+      </c>
+      <c r="G76" s="17">
+        <f>E76*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H76" s="17">
+        <f>E76*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I76" s="17">
+        <f>E76*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>50</v>
+      </c>
+      <c r="B77" s="17">
+        <f>Fluxo!$R$54</f>
+        <v/>
+      </c>
+      <c r="C77" s="17">
+        <f>IF(A77&lt;=Capital!$B$9,Capital!$B$12,IF(A77&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D77" s="17">
+        <f>IF(A77&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$54),0)</f>
+        <v/>
+      </c>
+      <c r="E77" s="17">
+        <f>B77-C77-D77</f>
+        <v/>
+      </c>
+      <c r="F77" s="17">
+        <f>F76+E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="17">
+        <f>E77*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H77" s="17">
+        <f>E77*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I77" s="17">
+        <f>E77*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>51</v>
+      </c>
+      <c r="B78" s="17">
+        <f>Fluxo!$R$55</f>
+        <v/>
+      </c>
+      <c r="C78" s="17">
+        <f>IF(A78&lt;=Capital!$B$9,Capital!$B$12,IF(A78&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D78" s="17">
+        <f>IF(A78&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$55),0)</f>
+        <v/>
+      </c>
+      <c r="E78" s="17">
+        <f>B78-C78-D78</f>
+        <v/>
+      </c>
+      <c r="F78" s="17">
+        <f>F77+E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="17">
+        <f>E78*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H78" s="17">
+        <f>E78*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I78" s="17">
+        <f>E78*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>52</v>
+      </c>
+      <c r="B79" s="17">
+        <f>Fluxo!$R$56</f>
+        <v/>
+      </c>
+      <c r="C79" s="17">
+        <f>IF(A79&lt;=Capital!$B$9,Capital!$B$12,IF(A79&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D79" s="17">
+        <f>IF(A79&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$56),0)</f>
+        <v/>
+      </c>
+      <c r="E79" s="17">
+        <f>B79-C79-D79</f>
+        <v/>
+      </c>
+      <c r="F79" s="17">
+        <f>F78+E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="17">
+        <f>E79*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>E79*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>E79*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>53</v>
+      </c>
+      <c r="B80" s="17">
+        <f>Fluxo!$R$57</f>
+        <v/>
+      </c>
+      <c r="C80" s="17">
+        <f>IF(A80&lt;=Capital!$B$9,Capital!$B$12,IF(A80&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D80" s="17">
+        <f>IF(A80&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$57),0)</f>
+        <v/>
+      </c>
+      <c r="E80" s="17">
+        <f>B80-C80-D80</f>
+        <v/>
+      </c>
+      <c r="F80" s="17">
+        <f>F79+E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="17">
+        <f>E80*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H80" s="17">
+        <f>E80*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I80" s="17">
+        <f>E80*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>54</v>
+      </c>
+      <c r="B81" s="17">
+        <f>Fluxo!$R$58</f>
+        <v/>
+      </c>
+      <c r="C81" s="17">
+        <f>IF(A81&lt;=Capital!$B$9,Capital!$B$12,IF(A81&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D81" s="17">
+        <f>IF(A81&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$58),0)</f>
+        <v/>
+      </c>
+      <c r="E81" s="17">
+        <f>B81-C81-D81</f>
+        <v/>
+      </c>
+      <c r="F81" s="17">
+        <f>F80+E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="17">
+        <f>E81*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H81" s="17">
+        <f>E81*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I81" s="17">
+        <f>E81*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>55</v>
+      </c>
+      <c r="B82" s="17">
+        <f>Fluxo!$R$59</f>
+        <v/>
+      </c>
+      <c r="C82" s="17">
+        <f>IF(A82&lt;=Capital!$B$9,Capital!$B$12,IF(A82&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D82" s="17">
+        <f>IF(A82&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$59),0)</f>
+        <v/>
+      </c>
+      <c r="E82" s="17">
+        <f>B82-C82-D82</f>
+        <v/>
+      </c>
+      <c r="F82" s="17">
+        <f>F81+E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="17">
+        <f>E82*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>E82*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>E82*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>56</v>
+      </c>
+      <c r="B83" s="17">
+        <f>Fluxo!$R$60</f>
+        <v/>
+      </c>
+      <c r="C83" s="17">
+        <f>IF(A83&lt;=Capital!$B$9,Capital!$B$12,IF(A83&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D83" s="17">
+        <f>IF(A83&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$60),0)</f>
+        <v/>
+      </c>
+      <c r="E83" s="17">
+        <f>B83-C83-D83</f>
+        <v/>
+      </c>
+      <c r="F83" s="17">
+        <f>F82+E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="17">
+        <f>E83*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H83" s="17">
+        <f>E83*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I83" s="17">
+        <f>E83*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>57</v>
+      </c>
+      <c r="B84" s="17">
+        <f>Fluxo!$R$61</f>
+        <v/>
+      </c>
+      <c r="C84" s="17">
+        <f>IF(A84&lt;=Capital!$B$9,Capital!$B$12,IF(A84&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D84" s="17">
+        <f>IF(A84&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$61),0)</f>
+        <v/>
+      </c>
+      <c r="E84" s="17">
+        <f>B84-C84-D84</f>
+        <v/>
+      </c>
+      <c r="F84" s="17">
+        <f>F83+E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="17">
+        <f>E84*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H84" s="17">
+        <f>E84*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I84" s="17">
+        <f>E84*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>58</v>
+      </c>
+      <c r="B85" s="17">
+        <f>Fluxo!$R$62</f>
+        <v/>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(A85&lt;=Capital!$B$9,Capital!$B$12,IF(A85&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(A85&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$62),0)</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>B85-C85-D85</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>F84+E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>E85*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>E85*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>E85*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>59</v>
+      </c>
+      <c r="B86" s="17">
+        <f>Fluxo!$R$63</f>
+        <v/>
+      </c>
+      <c r="C86" s="17">
+        <f>IF(A86&lt;=Capital!$B$9,Capital!$B$12,IF(A86&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))</f>
+        <v/>
+      </c>
+      <c r="D86" s="17">
+        <f>IF(A86&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$63),0)</f>
+        <v/>
+      </c>
+      <c r="E86" s="17">
+        <f>B86-C86-D86</f>
+        <v/>
+      </c>
+      <c r="F86" s="17">
+        <f>F85+E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="17">
+        <f>E86*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>E86*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>E86*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>60</v>
+      </c>
+      <c r="B87" s="17">
+        <f>Fluxo!$R$64</f>
+        <v/>
+      </c>
+      <c r="C87" s="17">
+        <f>IF(A87&lt;=Capital!$B$9,Capital!$B$12,IF(A87&lt;=Capital!$B$9+Capital!$B$8,Capital!$B$11,0))+Capital!$B$11*(1-(1+Capital!$B$10)^-MAX(0,Capital!$B$8-(60-Capital!$B$9)))/Capital!$B$10</f>
+        <v/>
+      </c>
+      <c r="D87" s="17">
+        <f>IF(A87&lt;=12,Capital!$B$15*87.0*(1-Fluxo!$K$64),0)</f>
+        <v/>
+      </c>
+      <c r="E87" s="17">
+        <f>B87-C87-D87</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>F86+E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="17">
+        <f>E87*Capital!$B$22</f>
+        <v/>
+      </c>
+      <c r="H87" s="17">
+        <f>E87*Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="I87" s="17">
+        <f>E87*(1-Capital!$B$22-Capital!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>RESULTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>CAPITAL A RESERVAR (pico de caixa)</t>
+        </is>
+      </c>
+      <c r="B91" s="15">
+        <f>-MIN(F27:F87)</f>
+        <v/>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>e isto, nao a 1a tranche, que precisa estar comprometido</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1a tranche, na assinatura</t>
+        </is>
+      </c>
+      <c r="B92" s="15">
+        <f>-E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a chamar durante a rampa</t>
+        </is>
+      </c>
+      <c r="B93" s="15">
+        <f>-MIN(F27:F87)+E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Mes do pico</t>
+        </is>
+      </c>
+      <c r="B94" s="26">
+        <f>MATCH(MIN(F27:F87),F27:F87,0)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>TIR do equity (a.a.)</t>
+        </is>
+      </c>
+      <c r="B95" s="27">
+        <f>IFERROR((1+IRR(E27:E87,0.02))^12-1,"n/d")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>VPL do equity na TMA</t>
+        </is>
+      </c>
+      <c r="B96" s="15">
+        <f>NPV((1+Premissas!$B$78)^(1/12)-1,E28:E87)+E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>TIR do investidor A</t>
+        </is>
+      </c>
+      <c r="B97" s="27">
+        <f>IFERROR((1+IRR(G27:G87,0.02))^12-1,"n/d")</f>
+        <v/>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>o que ele compara com o CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>TIR do investidor B</t>
+        </is>
+      </c>
+      <c r="B98" s="27">
+        <f>IFERROR((1+IRR(H27:H87,0.02))^12-1,"n/d")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>TIR do Antonio</t>
+        </is>
+      </c>
+      <c r="B99" s="27">
+        <f>IFERROR((1+IRR(I27:I87,0.02))^12-1,"n/d")</f>
+        <v/>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>mais o pro-labore e 100% da franqueadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Aporte do Antonio</t>
+        </is>
+      </c>
+      <c r="B100" s="15">
+        <f>-I27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Fatia do Antonio</t>
+        </is>
+      </c>
+      <c r="B101" s="27">
+        <f>1-Capital!$B$22-Capital!$B$24</f>
+        <v/>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>FIQUE ACIMA DE 50%: e a unidade padrao da rede</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>O aporte do Antonio e o residual: capital a reservar menos os aportes dos investidores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>As colunas dos socios lancam o compromisso inteiro no mes 0. Na pratica ele e chamado em tranches,</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>o que melhora a TIR deles - logo as TIRs aqui sao conservadoras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>A pre-venda e antecipacao de receita: entra no mes 0 e sai da receita dos 12 meses seguintes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1594,97 +4363,97 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Assinantes</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>% da frota</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Receita assin.</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Receita avulsa</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>Complementar</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Receita total</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Lavagens/mes</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Lavagens/dia</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="25" t="inlineStr">
         <is>
           <t>RBT12</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="25" t="inlineStr">
         <is>
           <t>Aliq. Simples</t>
         </is>
       </c>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="25" t="inlineStr">
         <is>
           <t>Imposto</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="25" t="inlineStr">
         <is>
           <t>Custo variavel</t>
         </is>
       </c>
-      <c r="N3" s="24" t="inlineStr">
+      <c r="N3" s="25" t="inlineStr">
         <is>
           <t>Custo fixo</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="25" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="P3" s="24" t="inlineStr">
+      <c r="P3" s="25" t="inlineStr">
         <is>
           <t>Margem</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="25" t="inlineStr">
         <is>
           <t>Capex manut.</t>
         </is>
       </c>
-      <c r="R3" s="24" t="inlineStr">
+      <c r="R3" s="25" t="inlineStr">
         <is>
           <t>Fluxo livre</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="25" t="inlineStr">
         <is>
           <t>Caixa acumulado</t>
         </is>
@@ -1695,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="16">
-        <f>-Premissas!$B$72</f>
+        <f>-Premissas!$B$75</f>
         <v/>
       </c>
       <c r="S4" s="16">
@@ -1756,7 +4525,7 @@
         <v/>
       </c>
       <c r="N5" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O5" s="17">
@@ -1768,7 +4537,7 @@
         <v/>
       </c>
       <c r="Q5" s="17">
-        <f>G5*Premissas!$B$76</f>
+        <f>G5*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R5" s="17">
@@ -1833,7 +4602,7 @@
         <v/>
       </c>
       <c r="N6" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O6" s="17">
@@ -1845,7 +4614,7 @@
         <v/>
       </c>
       <c r="Q6" s="17">
-        <f>G6*Premissas!$B$76</f>
+        <f>G6*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R6" s="17">
@@ -1910,7 +4679,7 @@
         <v/>
       </c>
       <c r="N7" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O7" s="17">
@@ -1922,7 +4691,7 @@
         <v/>
       </c>
       <c r="Q7" s="17">
-        <f>G7*Premissas!$B$76</f>
+        <f>G7*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R7" s="17">
@@ -1987,7 +4756,7 @@
         <v/>
       </c>
       <c r="N8" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O8" s="17">
@@ -1999,7 +4768,7 @@
         <v/>
       </c>
       <c r="Q8" s="17">
-        <f>G8*Premissas!$B$76</f>
+        <f>G8*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R8" s="17">
@@ -2064,7 +4833,7 @@
         <v/>
       </c>
       <c r="N9" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O9" s="17">
@@ -2076,7 +4845,7 @@
         <v/>
       </c>
       <c r="Q9" s="17">
-        <f>G9*Premissas!$B$76</f>
+        <f>G9*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R9" s="17">
@@ -2141,7 +4910,7 @@
         <v/>
       </c>
       <c r="N10" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O10" s="17">
@@ -2153,7 +4922,7 @@
         <v/>
       </c>
       <c r="Q10" s="17">
-        <f>G10*Premissas!$B$76</f>
+        <f>G10*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R10" s="17">
@@ -2218,7 +4987,7 @@
         <v/>
       </c>
       <c r="N11" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O11" s="17">
@@ -2230,7 +4999,7 @@
         <v/>
       </c>
       <c r="Q11" s="17">
-        <f>G11*Premissas!$B$76</f>
+        <f>G11*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R11" s="17">
@@ -2295,7 +5064,7 @@
         <v/>
       </c>
       <c r="N12" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O12" s="17">
@@ -2307,7 +5076,7 @@
         <v/>
       </c>
       <c r="Q12" s="17">
-        <f>G12*Premissas!$B$76</f>
+        <f>G12*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R12" s="17">
@@ -2372,7 +5141,7 @@
         <v/>
       </c>
       <c r="N13" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O13" s="17">
@@ -2384,7 +5153,7 @@
         <v/>
       </c>
       <c r="Q13" s="17">
-        <f>G13*Premissas!$B$76</f>
+        <f>G13*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R13" s="17">
@@ -2449,7 +5218,7 @@
         <v/>
       </c>
       <c r="N14" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O14" s="17">
@@ -2461,7 +5230,7 @@
         <v/>
       </c>
       <c r="Q14" s="17">
-        <f>G14*Premissas!$B$76</f>
+        <f>G14*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R14" s="17">
@@ -2526,7 +5295,7 @@
         <v/>
       </c>
       <c r="N15" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O15" s="17">
@@ -2538,7 +5307,7 @@
         <v/>
       </c>
       <c r="Q15" s="17">
-        <f>G15*Premissas!$B$76</f>
+        <f>G15*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R15" s="17">
@@ -2603,7 +5372,7 @@
         <v/>
       </c>
       <c r="N16" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O16" s="17">
@@ -2615,7 +5384,7 @@
         <v/>
       </c>
       <c r="Q16" s="17">
-        <f>G16*Premissas!$B$76</f>
+        <f>G16*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R16" s="17">
@@ -2680,7 +5449,7 @@
         <v/>
       </c>
       <c r="N17" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O17" s="17">
@@ -2692,7 +5461,7 @@
         <v/>
       </c>
       <c r="Q17" s="17">
-        <f>G17*Premissas!$B$76</f>
+        <f>G17*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R17" s="17">
@@ -2757,7 +5526,7 @@
         <v/>
       </c>
       <c r="N18" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O18" s="17">
@@ -2769,7 +5538,7 @@
         <v/>
       </c>
       <c r="Q18" s="17">
-        <f>G18*Premissas!$B$76</f>
+        <f>G18*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R18" s="17">
@@ -2834,7 +5603,7 @@
         <v/>
       </c>
       <c r="N19" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O19" s="17">
@@ -2846,7 +5615,7 @@
         <v/>
       </c>
       <c r="Q19" s="17">
-        <f>G19*Premissas!$B$76</f>
+        <f>G19*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R19" s="17">
@@ -2911,7 +5680,7 @@
         <v/>
       </c>
       <c r="N20" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O20" s="17">
@@ -2923,7 +5692,7 @@
         <v/>
       </c>
       <c r="Q20" s="17">
-        <f>G20*Premissas!$B$76</f>
+        <f>G20*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R20" s="17">
@@ -2988,7 +5757,7 @@
         <v/>
       </c>
       <c r="N21" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O21" s="17">
@@ -3000,7 +5769,7 @@
         <v/>
       </c>
       <c r="Q21" s="17">
-        <f>G21*Premissas!$B$76</f>
+        <f>G21*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R21" s="17">
@@ -3065,7 +5834,7 @@
         <v/>
       </c>
       <c r="N22" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O22" s="17">
@@ -3077,7 +5846,7 @@
         <v/>
       </c>
       <c r="Q22" s="17">
-        <f>G22*Premissas!$B$76</f>
+        <f>G22*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R22" s="17">
@@ -3142,7 +5911,7 @@
         <v/>
       </c>
       <c r="N23" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O23" s="17">
@@ -3154,7 +5923,7 @@
         <v/>
       </c>
       <c r="Q23" s="17">
-        <f>G23*Premissas!$B$76</f>
+        <f>G23*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R23" s="17">
@@ -3219,7 +5988,7 @@
         <v/>
       </c>
       <c r="N24" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O24" s="17">
@@ -3231,7 +6000,7 @@
         <v/>
       </c>
       <c r="Q24" s="17">
-        <f>G24*Premissas!$B$76</f>
+        <f>G24*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R24" s="17">
@@ -3296,7 +6065,7 @@
         <v/>
       </c>
       <c r="N25" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O25" s="17">
@@ -3308,7 +6077,7 @@
         <v/>
       </c>
       <c r="Q25" s="17">
-        <f>G25*Premissas!$B$76</f>
+        <f>G25*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R25" s="17">
@@ -3373,7 +6142,7 @@
         <v/>
       </c>
       <c r="N26" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O26" s="17">
@@ -3385,7 +6154,7 @@
         <v/>
       </c>
       <c r="Q26" s="17">
-        <f>G26*Premissas!$B$76</f>
+        <f>G26*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R26" s="17">
@@ -3450,7 +6219,7 @@
         <v/>
       </c>
       <c r="N27" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O27" s="17">
@@ -3462,7 +6231,7 @@
         <v/>
       </c>
       <c r="Q27" s="17">
-        <f>G27*Premissas!$B$76</f>
+        <f>G27*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R27" s="17">
@@ -3527,7 +6296,7 @@
         <v/>
       </c>
       <c r="N28" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O28" s="17">
@@ -3539,7 +6308,7 @@
         <v/>
       </c>
       <c r="Q28" s="17">
-        <f>G28*Premissas!$B$76</f>
+        <f>G28*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R28" s="17">
@@ -3604,7 +6373,7 @@
         <v/>
       </c>
       <c r="N29" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O29" s="17">
@@ -3616,7 +6385,7 @@
         <v/>
       </c>
       <c r="Q29" s="17">
-        <f>G29*Premissas!$B$76</f>
+        <f>G29*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R29" s="17">
@@ -3681,7 +6450,7 @@
         <v/>
       </c>
       <c r="N30" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O30" s="17">
@@ -3693,7 +6462,7 @@
         <v/>
       </c>
       <c r="Q30" s="17">
-        <f>G30*Premissas!$B$76</f>
+        <f>G30*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R30" s="17">
@@ -3758,7 +6527,7 @@
         <v/>
       </c>
       <c r="N31" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O31" s="17">
@@ -3770,7 +6539,7 @@
         <v/>
       </c>
       <c r="Q31" s="17">
-        <f>G31*Premissas!$B$76</f>
+        <f>G31*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R31" s="17">
@@ -3835,7 +6604,7 @@
         <v/>
       </c>
       <c r="N32" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O32" s="17">
@@ -3847,7 +6616,7 @@
         <v/>
       </c>
       <c r="Q32" s="17">
-        <f>G32*Premissas!$B$76</f>
+        <f>G32*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R32" s="17">
@@ -3912,7 +6681,7 @@
         <v/>
       </c>
       <c r="N33" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O33" s="17">
@@ -3924,7 +6693,7 @@
         <v/>
       </c>
       <c r="Q33" s="17">
-        <f>G33*Premissas!$B$76</f>
+        <f>G33*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R33" s="17">
@@ -3989,7 +6758,7 @@
         <v/>
       </c>
       <c r="N34" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O34" s="17">
@@ -4001,7 +6770,7 @@
         <v/>
       </c>
       <c r="Q34" s="17">
-        <f>G34*Premissas!$B$76</f>
+        <f>G34*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R34" s="17">
@@ -4066,7 +6835,7 @@
         <v/>
       </c>
       <c r="N35" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O35" s="17">
@@ -4078,7 +6847,7 @@
         <v/>
       </c>
       <c r="Q35" s="17">
-        <f>G35*Premissas!$B$76</f>
+        <f>G35*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R35" s="17">
@@ -4143,7 +6912,7 @@
         <v/>
       </c>
       <c r="N36" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O36" s="17">
@@ -4155,7 +6924,7 @@
         <v/>
       </c>
       <c r="Q36" s="17">
-        <f>G36*Premissas!$B$76</f>
+        <f>G36*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R36" s="17">
@@ -4220,7 +6989,7 @@
         <v/>
       </c>
       <c r="N37" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O37" s="17">
@@ -4232,7 +7001,7 @@
         <v/>
       </c>
       <c r="Q37" s="17">
-        <f>G37*Premissas!$B$76</f>
+        <f>G37*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R37" s="17">
@@ -4297,7 +7066,7 @@
         <v/>
       </c>
       <c r="N38" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O38" s="17">
@@ -4309,7 +7078,7 @@
         <v/>
       </c>
       <c r="Q38" s="17">
-        <f>G38*Premissas!$B$76</f>
+        <f>G38*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R38" s="17">
@@ -4374,7 +7143,7 @@
         <v/>
       </c>
       <c r="N39" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O39" s="17">
@@ -4386,7 +7155,7 @@
         <v/>
       </c>
       <c r="Q39" s="17">
-        <f>G39*Premissas!$B$76</f>
+        <f>G39*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R39" s="17">
@@ -4451,7 +7220,7 @@
         <v/>
       </c>
       <c r="N40" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O40" s="17">
@@ -4463,7 +7232,7 @@
         <v/>
       </c>
       <c r="Q40" s="17">
-        <f>G40*Premissas!$B$76</f>
+        <f>G40*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R40" s="17">
@@ -4528,7 +7297,7 @@
         <v/>
       </c>
       <c r="N41" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O41" s="17">
@@ -4540,7 +7309,7 @@
         <v/>
       </c>
       <c r="Q41" s="17">
-        <f>G41*Premissas!$B$76</f>
+        <f>G41*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R41" s="17">
@@ -4605,7 +7374,7 @@
         <v/>
       </c>
       <c r="N42" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O42" s="17">
@@ -4617,7 +7386,7 @@
         <v/>
       </c>
       <c r="Q42" s="17">
-        <f>G42*Premissas!$B$76</f>
+        <f>G42*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R42" s="17">
@@ -4682,7 +7451,7 @@
         <v/>
       </c>
       <c r="N43" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O43" s="17">
@@ -4694,7 +7463,7 @@
         <v/>
       </c>
       <c r="Q43" s="17">
-        <f>G43*Premissas!$B$76</f>
+        <f>G43*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R43" s="17">
@@ -4759,7 +7528,7 @@
         <v/>
       </c>
       <c r="N44" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O44" s="17">
@@ -4771,7 +7540,7 @@
         <v/>
       </c>
       <c r="Q44" s="17">
-        <f>G44*Premissas!$B$76</f>
+        <f>G44*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R44" s="17">
@@ -4836,7 +7605,7 @@
         <v/>
       </c>
       <c r="N45" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O45" s="17">
@@ -4848,7 +7617,7 @@
         <v/>
       </c>
       <c r="Q45" s="17">
-        <f>G45*Premissas!$B$76</f>
+        <f>G45*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R45" s="17">
@@ -4913,7 +7682,7 @@
         <v/>
       </c>
       <c r="N46" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O46" s="17">
@@ -4925,7 +7694,7 @@
         <v/>
       </c>
       <c r="Q46" s="17">
-        <f>G46*Premissas!$B$76</f>
+        <f>G46*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R46" s="17">
@@ -4990,7 +7759,7 @@
         <v/>
       </c>
       <c r="N47" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O47" s="17">
@@ -5002,7 +7771,7 @@
         <v/>
       </c>
       <c r="Q47" s="17">
-        <f>G47*Premissas!$B$76</f>
+        <f>G47*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R47" s="17">
@@ -5067,7 +7836,7 @@
         <v/>
       </c>
       <c r="N48" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O48" s="17">
@@ -5079,7 +7848,7 @@
         <v/>
       </c>
       <c r="Q48" s="17">
-        <f>G48*Premissas!$B$76</f>
+        <f>G48*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R48" s="17">
@@ -5144,7 +7913,7 @@
         <v/>
       </c>
       <c r="N49" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O49" s="17">
@@ -5156,7 +7925,7 @@
         <v/>
       </c>
       <c r="Q49" s="17">
-        <f>G49*Premissas!$B$76</f>
+        <f>G49*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R49" s="17">
@@ -5221,7 +7990,7 @@
         <v/>
       </c>
       <c r="N50" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O50" s="17">
@@ -5233,7 +8002,7 @@
         <v/>
       </c>
       <c r="Q50" s="17">
-        <f>G50*Premissas!$B$76</f>
+        <f>G50*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R50" s="17">
@@ -5298,7 +8067,7 @@
         <v/>
       </c>
       <c r="N51" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O51" s="17">
@@ -5310,7 +8079,7 @@
         <v/>
       </c>
       <c r="Q51" s="17">
-        <f>G51*Premissas!$B$76</f>
+        <f>G51*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R51" s="17">
@@ -5375,7 +8144,7 @@
         <v/>
       </c>
       <c r="N52" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O52" s="17">
@@ -5387,7 +8156,7 @@
         <v/>
       </c>
       <c r="Q52" s="17">
-        <f>G52*Premissas!$B$76</f>
+        <f>G52*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R52" s="17">
@@ -5452,7 +8221,7 @@
         <v/>
       </c>
       <c r="N53" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O53" s="17">
@@ -5464,7 +8233,7 @@
         <v/>
       </c>
       <c r="Q53" s="17">
-        <f>G53*Premissas!$B$76</f>
+        <f>G53*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R53" s="17">
@@ -5529,7 +8298,7 @@
         <v/>
       </c>
       <c r="N54" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O54" s="17">
@@ -5541,7 +8310,7 @@
         <v/>
       </c>
       <c r="Q54" s="17">
-        <f>G54*Premissas!$B$76</f>
+        <f>G54*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R54" s="17">
@@ -5606,7 +8375,7 @@
         <v/>
       </c>
       <c r="N55" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O55" s="17">
@@ -5618,7 +8387,7 @@
         <v/>
       </c>
       <c r="Q55" s="17">
-        <f>G55*Premissas!$B$76</f>
+        <f>G55*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R55" s="17">
@@ -5683,7 +8452,7 @@
         <v/>
       </c>
       <c r="N56" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O56" s="17">
@@ -5695,7 +8464,7 @@
         <v/>
       </c>
       <c r="Q56" s="17">
-        <f>G56*Premissas!$B$76</f>
+        <f>G56*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R56" s="17">
@@ -5760,7 +8529,7 @@
         <v/>
       </c>
       <c r="N57" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O57" s="17">
@@ -5772,7 +8541,7 @@
         <v/>
       </c>
       <c r="Q57" s="17">
-        <f>G57*Premissas!$B$76</f>
+        <f>G57*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R57" s="17">
@@ -5837,7 +8606,7 @@
         <v/>
       </c>
       <c r="N58" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O58" s="17">
@@ -5849,7 +8618,7 @@
         <v/>
       </c>
       <c r="Q58" s="17">
-        <f>G58*Premissas!$B$76</f>
+        <f>G58*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R58" s="17">
@@ -5914,7 +8683,7 @@
         <v/>
       </c>
       <c r="N59" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O59" s="17">
@@ -5926,7 +8695,7 @@
         <v/>
       </c>
       <c r="Q59" s="17">
-        <f>G59*Premissas!$B$76</f>
+        <f>G59*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R59" s="17">
@@ -5991,7 +8760,7 @@
         <v/>
       </c>
       <c r="N60" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O60" s="17">
@@ -6003,7 +8772,7 @@
         <v/>
       </c>
       <c r="Q60" s="17">
-        <f>G60*Premissas!$B$76</f>
+        <f>G60*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R60" s="17">
@@ -6068,7 +8837,7 @@
         <v/>
       </c>
       <c r="N61" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O61" s="17">
@@ -6080,7 +8849,7 @@
         <v/>
       </c>
       <c r="Q61" s="17">
-        <f>G61*Premissas!$B$76</f>
+        <f>G61*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R61" s="17">
@@ -6145,7 +8914,7 @@
         <v/>
       </c>
       <c r="N62" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O62" s="17">
@@ -6157,7 +8926,7 @@
         <v/>
       </c>
       <c r="Q62" s="17">
-        <f>G62*Premissas!$B$76</f>
+        <f>G62*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R62" s="17">
@@ -6222,7 +8991,7 @@
         <v/>
       </c>
       <c r="N63" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O63" s="17">
@@ -6234,7 +9003,7 @@
         <v/>
       </c>
       <c r="Q63" s="17">
-        <f>G63*Premissas!$B$76</f>
+        <f>G63*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R63" s="17">
@@ -6299,7 +9068,7 @@
         <v/>
       </c>
       <c r="N64" s="17">
-        <f>Premissas!$B$46</f>
+        <f>Premissas!$B$47</f>
         <v/>
       </c>
       <c r="O64" s="17">
@@ -6311,11 +9080,11 @@
         <v/>
       </c>
       <c r="Q64" s="17">
-        <f>G64*Premissas!$B$76</f>
+        <f>G64*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="R64" s="17">
-        <f>O64-Q64+Premissas!$B$63*Premissas!$B$77</f>
+        <f>O64-Q64+Premissas!$B$65*Premissas!$B$80</f>
         <v/>
       </c>
       <c r="S64" s="17">

--- a/docs/bp/Modelo-Economico-Piumhi.xlsx
+++ b/docs/bp/Modelo-Economico-Piumhi.xlsx
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ESTIMATIVA - confirmar com CEMIG</t>
+          <t>CONFIRMADO out/2026 - CEMIG baixa tensao</t>
         </is>
       </c>
     </row>

--- a/docs/bp/Modelo-Economico-Piumhi.xlsx
+++ b/docs/bp/Modelo-Economico-Piumhi.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ESTIMATIVA - confirmar com SAAE Piumhi</t>
+          <t>ESTIMATIVA - minimo de 30 m3 por R$ 93,59 confirmado; falta o excedente e o esgoto</t>
         </is>
       </c>
     </row>

--- a/docs/bp/Modelo-Economico-Piumhi.xlsx
+++ b/docs/bp/Modelo-Economico-Piumhi.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ESTIMATIVA - confirmar com SAAE Piumhi</t>
+          <t>ESTIMATIVA - minimo de 30 m3 por R$ 93,59 confirmado; falta o excedente e o esgoto</t>
         </is>
       </c>
     </row>
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ESTIMATIVA - confirmar com CEMIG</t>
+          <t>CONFIRMADO out/2026 - CEMIG baixa tensao</t>
         </is>
       </c>
     </row>

--- a/docs/bp/Modelo-Economico-Piumhi.xlsx
+++ b/docs/bp/Modelo-Economico-Piumhi.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1001,11 +1001,11 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Obra civil: portico, baia coberta, piso, patio 300 m2</t>
+          <t>Obra civil: portico, baia coberta, piso, patio 150 m2</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="54">
@@ -1041,7 +1041,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Totem de pagamento PIX/cartao + camera + CFTV + rede</t>
+          <t>Totem de pagamento PIX/cartao + camera de placa + CFTV</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -1051,276 +1051,266 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>1 box de alta pressao + 2 aspiradores</t>
+          <t>Fachada e comunicacao visual, versao simples</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Fachada, comunicacao visual, iluminacao</t>
+          <t>Software da unidade e implantacao</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>19000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Software da unidade, integracao e implantacao</t>
+          <t>Projeto, licencas, alvaras, bombeiros, taxas</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Projeto, licencas, alvaras, bombeiros, taxas</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>14000</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="B61" s="16">
+        <f>SUM(B51:B60)</f>
+        <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="B62" s="16">
-        <f>SUM(B51:B61)</f>
-        <v/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Contingencia (%)</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Contingencia (%)</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="n">
-        <v>0.08</v>
+          <t>Cortes da versao enxuta</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>71060</v>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>boxes e aspiradores no mes 6, patio de 150 m2, fachada simples; zere para o capex cheio</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Cortes da versao enxuta</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>71060</v>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>boxes e aspiradores no mes 6, patio de 150 m2, fachada simples; zere para o capex cheio</t>
-        </is>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CAPEX TOTAL</t>
+        </is>
+      </c>
+      <c r="B64" s="15">
+        <f>B61*(1+B62)-B63</f>
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>CAPEX TOTAL</t>
-        </is>
-      </c>
-      <c r="B65" s="15">
-        <f>B62*(1+B63)-B64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>do qual benfeitoria em imovel de terceiro</t>
         </is>
       </c>
-      <c r="B66" s="17">
+      <c r="B65" s="17">
         <f>B53+B54+B55</f>
         <v/>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>obra civil + separadora + entrada de energia</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CAPITAL DE GIRO</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>CAPITAL DE GIRO</t>
-        </is>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Caucao de 3 alugueis</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Caucao de 3 alugueis</t>
+          <t>Campanha de pre-venda e inauguracao</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Campanha de pre-venda e inauguracao</t>
+          <t>Estoque inicial de quimicos</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>22000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Estoque inicial de quimicos</t>
+          <t>Colchao de 3 meses de custo fixo</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>6000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Colchao de 3 meses de custo fixo</t>
+          <t>Cortes no giro (versao enxuta)</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>18000</v>
+        <v>10000</v>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>zere junto com os cortes do capex</t>
+        </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Cortes no giro (versao enxuta)</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>zere junto com os cortes do capex</t>
-        </is>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL GIRO</t>
+        </is>
+      </c>
+      <c r="B73" s="15">
+        <f>SUM(B68:B71)-B72</f>
+        <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL GIRO</t>
-        </is>
-      </c>
-      <c r="B74" s="15">
-        <f>SUM(B69:B72)-B73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>INVESTIMENTO TOTAL</t>
         </is>
       </c>
-      <c r="B75" s="19">
-        <f>B65+B74</f>
-        <v/>
+      <c r="B74" s="19">
+        <f>B64+B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>FINANCEIRO</t>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TMA (a.a.)</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Selic em ago/2026: 14% a.a.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>TMA (a.a.)</t>
+          <t>Capex de manutencao (% da receita)</t>
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Selic em ago/2026: 14% a.a.</t>
-        </is>
+        <v>0.015</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Capex de manutencao (% da receita)</t>
+          <t>Valor residual do capex no mes 60</t>
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Valor residual do capex no mes 60</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="n">
         <v>0.3</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CAPACIDADE</t>
+        </is>
+      </c>
+    </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>CAPACIDADE</t>
-        </is>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo + manobra (min)</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Ciclo + manobra (min)</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="n">
-        <v>6.5</v>
+          <t>Disponibilidade da maquina</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Disponibilidade da maquina</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="n">
-        <v>0.9</v>
+          <t>Janela diaria de pico (horas)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Janela diaria de pico (horas)</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
           <t>Lavagens na janela de pico</t>
         </is>
       </c>
-      <c r="B86" s="12" t="n">
+      <c r="B85" s="12" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1360,7 +1350,7 @@
         </is>
       </c>
       <c r="B3" s="19">
-        <f>Premissas!$B$75</f>
+        <f>Premissas!$B$74</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1361,7 @@
         </is>
       </c>
       <c r="B4" s="17">
-        <f>Premissas!$B$65</f>
+        <f>Premissas!$B$64</f>
         <v/>
       </c>
     </row>
@@ -1382,7 +1372,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Premissas!$B$74</f>
+        <f>Premissas!$B$73</f>
         <v/>
       </c>
     </row>
@@ -1393,7 +1383,7 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>Premissas!$B$66</f>
+        <f>Premissas!$B$65</f>
         <v/>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1469,7 +1459,7 @@
         </is>
       </c>
       <c r="B14" s="19">
-        <f>NPV((1+Premissas!$B$78)^(1/12)-1,Fluxo!$R$5:$R$64)+Fluxo!$R$4</f>
+        <f>NPV((1+Premissas!$B$77)^(1/12)-1,Fluxo!$R$5:$R$64)+Fluxo!$R$4</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1481,7 @@
         </is>
       </c>
       <c r="B16" s="21">
-        <f>SUM(Fluxo!$R$5:$R$64)/Premissas!$B$75</f>
+        <f>SUM(Fluxo!$R$5:$R$64)/Premissas!$B$74</f>
         <v/>
       </c>
     </row>
@@ -1560,7 +1550,7 @@
         </is>
       </c>
       <c r="B25" s="20">
-        <f>60/Premissas!$B$83*Premissas!$B$84*Premissas!$B$85/Premissas!$B$86</f>
+        <f>60/Premissas!$B$82*Premissas!$B$83*Premissas!$B$84/Premissas!$B$85</f>
         <v/>
       </c>
     </row>
@@ -4205,7 +4195,7 @@
         </is>
       </c>
       <c r="B96" s="15">
-        <f>NPV((1+Premissas!$B$78)^(1/12)-1,E28:E87)+E27</f>
+        <f>NPV((1+Premissas!$B$77)^(1/12)-1,E28:E87)+E27</f>
         <v/>
       </c>
     </row>
@@ -4464,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="16">
-        <f>-Premissas!$B$75</f>
+        <f>-Premissas!$B$74</f>
         <v/>
       </c>
       <c r="S4" s="16">
@@ -4537,7 +4527,7 @@
         <v/>
       </c>
       <c r="Q5" s="17">
-        <f>G5*Premissas!$B$79</f>
+        <f>G5*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R5" s="17">
@@ -4614,7 +4604,7 @@
         <v/>
       </c>
       <c r="Q6" s="17">
-        <f>G6*Premissas!$B$79</f>
+        <f>G6*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R6" s="17">
@@ -4691,7 +4681,7 @@
         <v/>
       </c>
       <c r="Q7" s="17">
-        <f>G7*Premissas!$B$79</f>
+        <f>G7*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R7" s="17">
@@ -4768,7 +4758,7 @@
         <v/>
       </c>
       <c r="Q8" s="17">
-        <f>G8*Premissas!$B$79</f>
+        <f>G8*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R8" s="17">
@@ -4845,7 +4835,7 @@
         <v/>
       </c>
       <c r="Q9" s="17">
-        <f>G9*Premissas!$B$79</f>
+        <f>G9*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R9" s="17">
@@ -4922,7 +4912,7 @@
         <v/>
       </c>
       <c r="Q10" s="17">
-        <f>G10*Premissas!$B$79</f>
+        <f>G10*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R10" s="17">
@@ -4999,7 +4989,7 @@
         <v/>
       </c>
       <c r="Q11" s="17">
-        <f>G11*Premissas!$B$79</f>
+        <f>G11*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R11" s="17">
@@ -5076,7 +5066,7 @@
         <v/>
       </c>
       <c r="Q12" s="17">
-        <f>G12*Premissas!$B$79</f>
+        <f>G12*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R12" s="17">
@@ -5153,7 +5143,7 @@
         <v/>
       </c>
       <c r="Q13" s="17">
-        <f>G13*Premissas!$B$79</f>
+        <f>G13*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R13" s="17">
@@ -5230,7 +5220,7 @@
         <v/>
       </c>
       <c r="Q14" s="17">
-        <f>G14*Premissas!$B$79</f>
+        <f>G14*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R14" s="17">
@@ -5307,7 +5297,7 @@
         <v/>
       </c>
       <c r="Q15" s="17">
-        <f>G15*Premissas!$B$79</f>
+        <f>G15*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R15" s="17">
@@ -5384,7 +5374,7 @@
         <v/>
       </c>
       <c r="Q16" s="17">
-        <f>G16*Premissas!$B$79</f>
+        <f>G16*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R16" s="17">
@@ -5461,7 +5451,7 @@
         <v/>
       </c>
       <c r="Q17" s="17">
-        <f>G17*Premissas!$B$79</f>
+        <f>G17*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R17" s="17">
@@ -5538,7 +5528,7 @@
         <v/>
       </c>
       <c r="Q18" s="17">
-        <f>G18*Premissas!$B$79</f>
+        <f>G18*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R18" s="17">
@@ -5615,7 +5605,7 @@
         <v/>
       </c>
       <c r="Q19" s="17">
-        <f>G19*Premissas!$B$79</f>
+        <f>G19*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R19" s="17">
@@ -5692,7 +5682,7 @@
         <v/>
       </c>
       <c r="Q20" s="17">
-        <f>G20*Premissas!$B$79</f>
+        <f>G20*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R20" s="17">
@@ -5769,7 +5759,7 @@
         <v/>
       </c>
       <c r="Q21" s="17">
-        <f>G21*Premissas!$B$79</f>
+        <f>G21*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R21" s="17">
@@ -5846,7 +5836,7 @@
         <v/>
       </c>
       <c r="Q22" s="17">
-        <f>G22*Premissas!$B$79</f>
+        <f>G22*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R22" s="17">
@@ -5923,7 +5913,7 @@
         <v/>
       </c>
       <c r="Q23" s="17">
-        <f>G23*Premissas!$B$79</f>
+        <f>G23*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R23" s="17">
@@ -6000,7 +5990,7 @@
         <v/>
       </c>
       <c r="Q24" s="17">
-        <f>G24*Premissas!$B$79</f>
+        <f>G24*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R24" s="17">
@@ -6077,7 +6067,7 @@
         <v/>
       </c>
       <c r="Q25" s="17">
-        <f>G25*Premissas!$B$79</f>
+        <f>G25*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R25" s="17">
@@ -6154,7 +6144,7 @@
         <v/>
       </c>
       <c r="Q26" s="17">
-        <f>G26*Premissas!$B$79</f>
+        <f>G26*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R26" s="17">
@@ -6231,7 +6221,7 @@
         <v/>
       </c>
       <c r="Q27" s="17">
-        <f>G27*Premissas!$B$79</f>
+        <f>G27*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R27" s="17">
@@ -6308,7 +6298,7 @@
         <v/>
       </c>
       <c r="Q28" s="17">
-        <f>G28*Premissas!$B$79</f>
+        <f>G28*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R28" s="17">
@@ -6385,7 +6375,7 @@
         <v/>
       </c>
       <c r="Q29" s="17">
-        <f>G29*Premissas!$B$79</f>
+        <f>G29*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R29" s="17">
@@ -6462,7 +6452,7 @@
         <v/>
       </c>
       <c r="Q30" s="17">
-        <f>G30*Premissas!$B$79</f>
+        <f>G30*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R30" s="17">
@@ -6539,7 +6529,7 @@
         <v/>
       </c>
       <c r="Q31" s="17">
-        <f>G31*Premissas!$B$79</f>
+        <f>G31*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R31" s="17">
@@ -6616,7 +6606,7 @@
         <v/>
       </c>
       <c r="Q32" s="17">
-        <f>G32*Premissas!$B$79</f>
+        <f>G32*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R32" s="17">
@@ -6693,7 +6683,7 @@
         <v/>
       </c>
       <c r="Q33" s="17">
-        <f>G33*Premissas!$B$79</f>
+        <f>G33*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R33" s="17">
@@ -6770,7 +6760,7 @@
         <v/>
       </c>
       <c r="Q34" s="17">
-        <f>G34*Premissas!$B$79</f>
+        <f>G34*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R34" s="17">
@@ -6847,7 +6837,7 @@
         <v/>
       </c>
       <c r="Q35" s="17">
-        <f>G35*Premissas!$B$79</f>
+        <f>G35*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R35" s="17">
@@ -6924,7 +6914,7 @@
         <v/>
       </c>
       <c r="Q36" s="17">
-        <f>G36*Premissas!$B$79</f>
+        <f>G36*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R36" s="17">
@@ -7001,7 +6991,7 @@
         <v/>
       </c>
       <c r="Q37" s="17">
-        <f>G37*Premissas!$B$79</f>
+        <f>G37*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R37" s="17">
@@ -7078,7 +7068,7 @@
         <v/>
       </c>
       <c r="Q38" s="17">
-        <f>G38*Premissas!$B$79</f>
+        <f>G38*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R38" s="17">
@@ -7155,7 +7145,7 @@
         <v/>
       </c>
       <c r="Q39" s="17">
-        <f>G39*Premissas!$B$79</f>
+        <f>G39*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R39" s="17">
@@ -7232,7 +7222,7 @@
         <v/>
       </c>
       <c r="Q40" s="17">
-        <f>G40*Premissas!$B$79</f>
+        <f>G40*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R40" s="17">
@@ -7309,7 +7299,7 @@
         <v/>
       </c>
       <c r="Q41" s="17">
-        <f>G41*Premissas!$B$79</f>
+        <f>G41*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R41" s="17">
@@ -7386,7 +7376,7 @@
         <v/>
       </c>
       <c r="Q42" s="17">
-        <f>G42*Premissas!$B$79</f>
+        <f>G42*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R42" s="17">
@@ -7463,7 +7453,7 @@
         <v/>
       </c>
       <c r="Q43" s="17">
-        <f>G43*Premissas!$B$79</f>
+        <f>G43*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R43" s="17">
@@ -7540,7 +7530,7 @@
         <v/>
       </c>
       <c r="Q44" s="17">
-        <f>G44*Premissas!$B$79</f>
+        <f>G44*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R44" s="17">
@@ -7617,7 +7607,7 @@
         <v/>
       </c>
       <c r="Q45" s="17">
-        <f>G45*Premissas!$B$79</f>
+        <f>G45*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R45" s="17">
@@ -7694,7 +7684,7 @@
         <v/>
       </c>
       <c r="Q46" s="17">
-        <f>G46*Premissas!$B$79</f>
+        <f>G46*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R46" s="17">
@@ -7771,7 +7761,7 @@
         <v/>
       </c>
       <c r="Q47" s="17">
-        <f>G47*Premissas!$B$79</f>
+        <f>G47*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R47" s="17">
@@ -7848,7 +7838,7 @@
         <v/>
       </c>
       <c r="Q48" s="17">
-        <f>G48*Premissas!$B$79</f>
+        <f>G48*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R48" s="17">
@@ -7925,7 +7915,7 @@
         <v/>
       </c>
       <c r="Q49" s="17">
-        <f>G49*Premissas!$B$79</f>
+        <f>G49*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R49" s="17">
@@ -8002,7 +7992,7 @@
         <v/>
       </c>
       <c r="Q50" s="17">
-        <f>G50*Premissas!$B$79</f>
+        <f>G50*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R50" s="17">
@@ -8079,7 +8069,7 @@
         <v/>
       </c>
       <c r="Q51" s="17">
-        <f>G51*Premissas!$B$79</f>
+        <f>G51*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R51" s="17">
@@ -8156,7 +8146,7 @@
         <v/>
       </c>
       <c r="Q52" s="17">
-        <f>G52*Premissas!$B$79</f>
+        <f>G52*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R52" s="17">
@@ -8233,7 +8223,7 @@
         <v/>
       </c>
       <c r="Q53" s="17">
-        <f>G53*Premissas!$B$79</f>
+        <f>G53*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R53" s="17">
@@ -8310,7 +8300,7 @@
         <v/>
       </c>
       <c r="Q54" s="17">
-        <f>G54*Premissas!$B$79</f>
+        <f>G54*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R54" s="17">
@@ -8387,7 +8377,7 @@
         <v/>
       </c>
       <c r="Q55" s="17">
-        <f>G55*Premissas!$B$79</f>
+        <f>G55*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R55" s="17">
@@ -8464,7 +8454,7 @@
         <v/>
       </c>
       <c r="Q56" s="17">
-        <f>G56*Premissas!$B$79</f>
+        <f>G56*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R56" s="17">
@@ -8541,7 +8531,7 @@
         <v/>
       </c>
       <c r="Q57" s="17">
-        <f>G57*Premissas!$B$79</f>
+        <f>G57*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R57" s="17">
@@ -8618,7 +8608,7 @@
         <v/>
       </c>
       <c r="Q58" s="17">
-        <f>G58*Premissas!$B$79</f>
+        <f>G58*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R58" s="17">
@@ -8695,7 +8685,7 @@
         <v/>
       </c>
       <c r="Q59" s="17">
-        <f>G59*Premissas!$B$79</f>
+        <f>G59*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R59" s="17">
@@ -8772,7 +8762,7 @@
         <v/>
       </c>
       <c r="Q60" s="17">
-        <f>G60*Premissas!$B$79</f>
+        <f>G60*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R60" s="17">
@@ -8849,7 +8839,7 @@
         <v/>
       </c>
       <c r="Q61" s="17">
-        <f>G61*Premissas!$B$79</f>
+        <f>G61*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R61" s="17">
@@ -8926,7 +8916,7 @@
         <v/>
       </c>
       <c r="Q62" s="17">
-        <f>G62*Premissas!$B$79</f>
+        <f>G62*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R62" s="17">
@@ -9003,7 +8993,7 @@
         <v/>
       </c>
       <c r="Q63" s="17">
-        <f>G63*Premissas!$B$79</f>
+        <f>G63*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R63" s="17">
@@ -9080,11 +9070,11 @@
         <v/>
       </c>
       <c r="Q64" s="17">
-        <f>G64*Premissas!$B$79</f>
+        <f>G64*Premissas!$B$78</f>
         <v/>
       </c>
       <c r="R64" s="17">
-        <f>O64-Q64+Premissas!$B$65*Premissas!$B$80</f>
+        <f>O64-Q64+Premissas!$B$64*Premissas!$B$79</f>
         <v/>
       </c>
       <c r="S64" s="17">
